--- a/output/pdf_financials_xlsx/PRR.xlsx
+++ b/output/pdf_financials_xlsx/PRR.xlsx
@@ -615,7 +615,7 @@
         <v>0</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.106252</v>
       </c>
     </row>
     <row r="13">
@@ -867,7 +867,7 @@
         <v>-2.636123</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-2.027597</v>
+        <v>-2.133849</v>
       </c>
     </row>
     <row r="28">
@@ -899,7 +899,7 @@
         <v>-2.480906</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-1.893652</v>
+        <v>-1.999904</v>
       </c>
     </row>
     <row r="30">
@@ -976,13 +976,13 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>1.394027</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.057741</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.672522</v>
       </c>
     </row>
     <row r="35">
@@ -1008,13 +1008,13 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>1.394027</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>4.17251</v>
+        <v>4.230251</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>1.643456</v>
+        <v>2.315978</v>
       </c>
     </row>
     <row r="37">
@@ -1200,13 +1200,13 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>1.900586</v>
+        <v>0.506559</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.874391</v>
+        <v>0.81665</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.767459</v>
+        <v>0.09493699999999999</v>
       </c>
     </row>
     <row r="49">
@@ -2427,13 +2427,13 @@
         </is>
       </c>
       <c r="B124" s="3" t="n">
-        <v>0</v>
+        <v>-0.067828</v>
       </c>
       <c r="C124" s="3" t="n">
-        <v>0</v>
+        <v>-0.084832</v>
       </c>
       <c r="D124" s="3" t="n">
-        <v>0</v>
+        <v>-0.148612</v>
       </c>
     </row>
     <row r="125">
@@ -2443,13 +2443,13 @@
         </is>
       </c>
       <c r="B125" s="3" t="n">
-        <v>0</v>
+        <v>-0.067828</v>
       </c>
       <c r="C125" s="3" t="n">
-        <v>0</v>
+        <v>-0.084832</v>
       </c>
       <c r="D125" s="3" t="n">
-        <v>0</v>
+        <v>-0.148612</v>
       </c>
     </row>
     <row r="126">
@@ -2693,7 +2693,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">
@@ -2879,7 +2879,11 @@
           <t>Reclamation deposits (Note 9)</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr"/>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E8" s="5" t="n">
         <v>0.0595</v>
       </c>
@@ -4055,7 +4059,11 @@
           <t>Lease payments</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr"/>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E46" s="5" t="n">
         <v>-0.067828</v>
       </c>
@@ -5742,7 +5750,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">

--- a/output/pdf_financials_xlsx/PRR.xlsx
+++ b/output/pdf_financials_xlsx/PRR.xlsx
@@ -529,13 +529,13 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>0.634484</v>
+        <v>0.674484</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>0.710097</v>
+        <v>0.764097</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>0.783944</v>
+        <v>0.847944</v>
       </c>
     </row>
     <row r="8">
@@ -2219,10 +2219,10 @@
         </is>
       </c>
       <c r="B111" s="3" t="n">
-        <v>0</v>
+        <v>-0.09150899999999999</v>
       </c>
       <c r="C111" s="3" t="n">
-        <v>0</v>
+        <v>-0.00696</v>
       </c>
       <c r="D111" s="3" t="n">
         <v>0</v>
@@ -2593,10 +2593,10 @@
         </is>
       </c>
       <c r="B134" s="3" t="n">
-        <v>0</v>
+        <v>-0.09150899999999999</v>
       </c>
       <c r="C134" s="3" t="n">
-        <v>0</v>
+        <v>-0.00696</v>
       </c>
       <c r="D134" s="3" t="n">
         <v>0</v>
@@ -2609,10 +2609,10 @@
         </is>
       </c>
       <c r="B135" s="3" t="n">
-        <v>-1.574124</v>
+        <v>-1.665633</v>
       </c>
       <c r="C135" s="3" t="n">
-        <v>-2.053525</v>
+        <v>-2.060485</v>
       </c>
       <c r="D135" s="3" t="n">
         <v>-1.77638</v>
@@ -3900,7 +3900,11 @@
           <t>Acquisition of equipment</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr"/>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E41" s="5" t="n">
         <v>-0.09150899999999999</v>
       </c>
@@ -5340,7 +5344,11 @@
           <t>Directors’ fees (Note 11)</t>
         </is>
       </c>
-      <c r="D87" t="inlineStr"/>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E87" s="5" t="n">
         <v>0.04</v>
       </c>
